--- a/product_upload/packages/34/file.xlsx
+++ b/product_upload/packages/34/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -840,6 +845,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>TANDO 5 mg Film Coted Tablet</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-3B16BE504D6F</t>
         </is>
       </c>
@@ -863,7 +873,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1030,6 +1040,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>TANDO 20 mg Film Coted Tablet</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-94A4EC3D5DCB</t>
         </is>
       </c>
@@ -1053,7 +1068,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1220,6 +1235,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>XIGDUO XR 10 mg/1000 mg Film Coted Tablet</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-58C5DF304D84</t>
         </is>
       </c>
@@ -1243,7 +1263,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1406,6 +1426,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>ORATANE 10 mg Soft Capsules</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-CE775CA8D579</t>
         </is>
       </c>
@@ -1429,7 +1454,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1604,6 +1629,11 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>NOSTIFIX 0.5 mg TABLET</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-A60342D4684A</t>
         </is>
       </c>
@@ -1627,7 +1657,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1798,6 +1828,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>NOSTIFIX 0.5 mg TABLET</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-C8284E7AB052</t>
         </is>
       </c>
@@ -1821,7 +1856,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1984,6 +2019,11 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>ZOLONIA 5 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-30CAEBDA753A</t>
         </is>
       </c>
@@ -2007,7 +2047,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2170,6 +2210,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>ZOLONIA 10 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-61F695493D9F</t>
         </is>
       </c>
@@ -2193,7 +2238,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2364,6 +2409,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>YASMIN TAB.</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-D3DEFCFB5E3A</t>
         </is>
       </c>
@@ -2387,7 +2437,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2554,6 +2604,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>XIGDUO XR 10 mg/500 mg Film Coted Tablet</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-79356EB280C0</t>
         </is>
       </c>
@@ -2577,7 +2632,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2744,6 +2799,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>XIGDUO XR 5 mg/1000 mg Film Coted Tablet</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-CA700D6B9840</t>
         </is>
       </c>
@@ -2767,7 +2827,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2926,6 +2986,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>ORATANE 20 mg Soft Capsules</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-01E67604D366</t>
         </is>
       </c>
@@ -2949,7 +3014,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3112,6 +3177,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>CERUXIM 500 mg Film Coted Tablet</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-4CE8E899DB00</t>
         </is>
       </c>
@@ -3135,7 +3205,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3302,6 +3372,11 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>VILTIN 50 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-EB5C90D3BBA9</t>
         </is>
       </c>
@@ -3325,7 +3400,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3492,6 +3567,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>EXTEMENT 25 mg Chewable Tablet</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-35DA3E2F3B0A</t>
         </is>
       </c>
@@ -3515,7 +3595,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3686,6 +3766,11 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>SOLIQUA SOLOSTAR (33 mcg/ml) /100 U Solution for Injection</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-79A598228FB0</t>
         </is>
       </c>
@@ -3709,7 +3794,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3884,6 +3969,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>SOLIQUA SOLOSTAR (33 mcg/ml) /100 U Solution for Injection</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-68F79B7D115D</t>
         </is>
       </c>
@@ -3907,7 +3997,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4074,6 +4164,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>SOLIQUA SOLOSTAR 50 mcg/ml) /100 U Solution for Injection</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-EA24E58D4A2E</t>
         </is>
       </c>
@@ -4097,7 +4192,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4276,6 +4371,11 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>SOLIQUA SOLOSTAR 50 mcg/ml) /100 U Solution for Injection</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-2E36F84C8664</t>
         </is>
       </c>
@@ -4299,7 +4399,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4470,6 +4570,11 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>ARPENIA 1 mg/ml Oral Solution</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-8358E3F9DCCF</t>
         </is>
       </c>
@@ -4493,7 +4598,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4658,6 +4763,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>INSTIGAR 30 mg Delayed-Release Capsule</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-556157F68317</t>
         </is>
       </c>
@@ -4681,7 +4791,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4854,6 +4964,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>INSTIGAR 30 mg Delayed-Release Capsule</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-1651BB792BC9</t>
         </is>
       </c>
@@ -4877,7 +4992,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5042,6 +5157,11 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>EZEACT 40 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-E4DBB167AED6</t>
         </is>
       </c>
@@ -5065,7 +5185,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5222,6 +5342,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>EZEACT 80 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-91EED65F5453</t>
         </is>
       </c>
@@ -5245,7 +5370,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5416,6 +5541,11 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>ARENA PLUS 150 mg/12.5 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-4680D2984C72</t>
         </is>
       </c>
@@ -5439,7 +5569,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5606,6 +5736,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>ARENA PLUS 300 mg/12.5 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-58256C55D65F</t>
         </is>
       </c>
@@ -5629,7 +5764,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5796,6 +5931,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>ARENA PLUS 300 mg/25 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-237D7FC349F2</t>
         </is>
       </c>
@@ -5819,7 +5959,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5996,6 +6136,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>INSTIGAR 60 mg Delayed-Release Capsule</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-271E63750E71</t>
         </is>
       </c>
@@ -6019,7 +6164,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6190,6 +6335,11 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>ACTODRYL Syrup</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-4D5845EA88DC</t>
         </is>
       </c>
@@ -6213,7 +6363,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6380,6 +6530,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>EXTEMENT 50 mg Chewable Tablet</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-612AED0B1F4A</t>
         </is>
       </c>
@@ -6403,7 +6558,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6570,6 +6725,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>EXTEMENT 100 mg Chewable Tablet</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-0C57C8280305</t>
         </is>
       </c>
@@ -6593,7 +6753,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6756,6 +6916,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>IRBEGEN 150 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-3B5C73EF9F1D</t>
         </is>
       </c>
@@ -6779,7 +6944,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6942,6 +7107,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>IRBEGEN 300 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-3DC5F6B2BB33</t>
         </is>
       </c>
@@ -6965,7 +7135,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7132,6 +7302,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>SEROGEN 25 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-EC705EFCBBF9</t>
         </is>
       </c>
@@ -7155,7 +7330,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7326,6 +7501,11 @@
       </c>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>SEROGEN 100 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-7C3E7BAB0600</t>
         </is>
       </c>
@@ -7349,7 +7529,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7516,6 +7696,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>SEROGEN 200 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-F86972D32035</t>
         </is>
       </c>
@@ -7539,7 +7724,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7702,6 +7887,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>SEROGEN 300 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-1E3F14FDE8EF</t>
         </is>
       </c>
@@ -7725,7 +7915,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7896,6 +8086,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>LAYAL Syrup</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-3E02DBBCCA4A</t>
         </is>
       </c>
@@ -7919,7 +8114,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8098,6 +8293,11 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
+          <t xml:space="preserve">BASAGLAR 100 u/ml solution for injection in Pre-Filled pen	</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-ECFD441B59CE</t>
         </is>
       </c>
@@ -8121,7 +8321,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8292,6 +8492,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>JADENU 90 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-31392A52954A</t>
         </is>
       </c>
@@ -8315,7 +8520,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8482,6 +8687,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>JADENU 180 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-8EB9F8F33FDE</t>
         </is>
       </c>
@@ -8505,7 +8715,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8672,6 +8882,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>JADENU 360 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-217894E3DC18</t>
         </is>
       </c>
@@ -8695,7 +8910,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8862,6 +9077,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>RECUGEL Eye Gel</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-D33BEA772E04</t>
         </is>
       </c>
@@ -8885,7 +9105,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -9044,6 +9264,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>AMEP 5 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-5BE49031AE27</t>
         </is>
       </c>
@@ -9067,7 +9292,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9234,6 +9459,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>BETOPTIC OPTHALMIC SOLUTION 0.5%</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-32610E15BC1A</t>
         </is>
       </c>
@@ -9257,7 +9487,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9424,6 +9654,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>TOBRADEX EYE OINT</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-B732E6BF64B8</t>
         </is>
       </c>
@@ -9447,7 +9682,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9606,6 +9841,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>OCUDINE 0.2%  OPHTHALMIC SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-D37294DE48E3</t>
         </is>
       </c>
@@ -9629,7 +9869,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9792,6 +10032,11 @@
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>NOSTAM 0.4 MG PROLONGED RELEASE TABLET</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-27E5FA67B13E</t>
         </is>
       </c>
@@ -9815,7 +10060,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9982,6 +10227,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>RAMEP 20 MG GASTRO-RESISTANT TABLET</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-0CB82530CC75</t>
         </is>
       </c>
@@ -10005,7 +10255,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10176,6 +10426,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>HEMLIBRA 150 MG/ML SOLUTION FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-3365D9D8686B</t>
         </is>
       </c>
@@ -10199,7 +10454,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10370,6 +10625,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>HEMLIBRA 150 MG/ML SOLUTION FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-ABD915E2D3F6</t>
         </is>
       </c>
@@ -10393,7 +10653,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10556,6 +10816,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>HEMLIBRA 150 MG/ML SOLUTION FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-5990D1751DB7</t>
         </is>
       </c>
@@ -10579,7 +10844,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10754,6 +11019,11 @@
       </c>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>HEMLIBRA 30 MG/ML SOLUTION FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-DF75AB1CD631</t>
         </is>
       </c>
@@ -10777,7 +11047,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10940,6 +11210,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>ZOLAN 10 MG FILM-COATED  TABLET</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-9D811F6FE55A</t>
         </is>
       </c>
@@ -10963,7 +11238,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11126,6 +11401,11 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>ZOLAN 5 MG FILM-COATED  TABLET</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-92BC1851B888</t>
         </is>
       </c>
@@ -11149,7 +11429,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11316,6 +11596,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>AQUAFLAM 50 MG SACHET</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-F2B967A546A9</t>
         </is>
       </c>
@@ -11339,7 +11624,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11502,6 +11787,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>BIOSOFT EYE DROP</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-71EA9AB8DF61</t>
         </is>
       </c>
@@ -11525,7 +11815,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11688,6 +11978,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>BIOSOFT PLUS EYE DROP</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-9DB2FD4E630F</t>
         </is>
       </c>
@@ -11711,7 +12006,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11870,6 +12165,11 @@
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>CHLORASEPTIC SORE THROAT LOZENGES (cherry)</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-44542946849A</t>
         </is>
       </c>
@@ -11893,7 +12193,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12060,6 +12360,11 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>CHLORASEPTIC SORE THROAT LOZENGES (citrus)</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-0EA9B72CBCF8</t>
         </is>
       </c>
@@ -12083,7 +12388,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12242,6 +12547,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>CHLORASEPTIC SORE THROAT LOZENGES ( Lemon)</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-5856A5EB2EA6</t>
         </is>
       </c>
@@ -12265,7 +12575,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12432,6 +12742,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>VERZENIO 200 MG FILM-COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-05D769A2EF61</t>
         </is>
       </c>
@@ -12455,7 +12770,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12626,6 +12941,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>VERZENIO 150 MG FILM-COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-173216398DEE</t>
         </is>
       </c>
@@ -12649,7 +12969,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12824,6 +13144,11 @@
       </c>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>VERZENIO 100 MG FILM-COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-82586CFCB334</t>
         </is>
       </c>
@@ -12847,7 +13172,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -13018,6 +13343,11 @@
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>VERZENIO 50 MG FILM-COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-D73333AC5BAA</t>
         </is>
       </c>
@@ -13041,7 +13371,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13204,6 +13534,11 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>VELIZA  500MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-82DB03CB30E0</t>
         </is>
       </c>
@@ -13227,7 +13562,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13400,6 +13735,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>CLEXANE 40MG\0.4ML PREFILLED SYRINGE</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-4D162D8FB66A</t>
         </is>
       </c>
@@ -13423,7 +13763,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13582,6 +13922,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>M.M.R II 0.5ML VACCINE+ 0.7ML DILUENT</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-C7CA90B83055</t>
         </is>
       </c>
@@ -13605,7 +13950,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13776,6 +14121,11 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>ARCOXIA 60MG TAB</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-18A6A074999F</t>
         </is>
       </c>
@@ -13799,7 +14149,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13970,6 +14320,11 @@
       </c>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>ARCOXIA 90MG TAB</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-3FB1ED1871AA</t>
         </is>
       </c>
@@ -13993,7 +14348,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14144,6 +14499,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>Z FILL DEEP 2 IMPLANT IN PRE-FILLED SYRINGE</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-99850E08F729</t>
         </is>
       </c>
@@ -14167,7 +14527,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14340,6 +14700,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>CLEXANE 80MG\0.8ML PREFILLED SYRINGE</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-B8FEC028CD7A</t>
         </is>
       </c>
@@ -14363,7 +14728,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14536,6 +14901,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>DEXILANT 30 mg</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-64166FC098DA</t>
         </is>
       </c>
@@ -14559,7 +14929,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14734,6 +15104,11 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>SOOLANTRA 10MG/GM CREAM</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-4E07856739BA</t>
         </is>
       </c>
@@ -14757,7 +15132,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14920,6 +15295,11 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>CARPAZIO 150 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-8C85CD531867</t>
         </is>
       </c>
@@ -14943,7 +15323,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15114,6 +15494,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>CARPAZIO 300 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-A9B287A7485B</t>
         </is>
       </c>
@@ -15137,7 +15522,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15304,6 +15689,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>CARPAZIO 600 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-193E834A8CFA</t>
         </is>
       </c>
@@ -15327,7 +15717,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15490,6 +15880,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>VIBERZI 100 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-938E4F344AB3</t>
         </is>
       </c>
@@ -15513,7 +15908,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15676,6 +16071,11 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>VIBERZI 75MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-EB94428F669D</t>
         </is>
       </c>
@@ -15699,7 +16099,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15862,6 +16262,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>VELPHORO 500 MG CHEWABLE TABLET</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-77B15D16FEB2</t>
         </is>
       </c>
@@ -15885,7 +16290,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -16050,6 +16455,11 @@
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>DEXILANT 30 mg</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-30DA1F194781</t>
         </is>
       </c>
@@ -16073,7 +16483,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16224,6 +16634,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>Z FILL CONTOUR 2 IMPLANT IN PRE-FILLED SYRINGE</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-67E893C786F5</t>
         </is>
       </c>
@@ -16247,7 +16662,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16402,6 +16817,11 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>Z FILL REFRESH 2 IMPLANT IN PRE-FILLED SYRINGE</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-C1B2D5B34F01</t>
         </is>
       </c>
@@ -16425,7 +16845,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16584,6 +17004,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>ESCITALAX 20MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-B6471E8E942B</t>
         </is>
       </c>
@@ -16607,7 +17032,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16766,6 +17191,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>ESCITALAX 15MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-CADDF4B7D946</t>
         </is>
       </c>
@@ -16789,7 +17219,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16948,6 +17378,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>ESCITALAX 10MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-855BA511A11D</t>
         </is>
       </c>
@@ -16971,7 +17406,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17142,6 +17577,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>LIPIZET 10MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-7402C3F62E7E</t>
         </is>
       </c>
@@ -17165,7 +17605,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17324,6 +17764,11 @@
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>Arkator 60MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-D044995FA711</t>
         </is>
       </c>
@@ -17347,7 +17792,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17506,6 +17951,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>Arkator 90MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-6D4DA7E99485</t>
         </is>
       </c>
@@ -17529,7 +17979,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17688,6 +18138,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>Arkator 120MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-48424CA6D883</t>
         </is>
       </c>
@@ -17711,7 +18166,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17870,6 +18325,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>STORVAS 40MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-F4031C8BFEE7</t>
         </is>
       </c>
@@ -17893,7 +18353,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -18052,6 +18512,11 @@
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>STORVAS 20MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-CD1D7BD2FFB3</t>
         </is>
       </c>
@@ -18075,7 +18540,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18238,6 +18703,11 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>STORVAS 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-2D4C122A114F</t>
         </is>
       </c>
@@ -18261,7 +18731,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18420,6 +18890,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>EPIXX 100MG/ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-7F1DEE481DCD</t>
         </is>
       </c>
@@ -18443,7 +18918,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18610,6 +19085,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>MUCOSOLVAN LA 75MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-9B65F910F841</t>
         </is>
       </c>
@@ -18633,7 +19113,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18804,6 +19284,11 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>UNISIA 8 MG/2.5 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-1D0040884E96</t>
         </is>
       </c>
@@ -18827,7 +19312,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18998,6 +19483,11 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>UNISIA 8 MG/5MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-0C3141F2D335</t>
         </is>
       </c>
@@ -19021,7 +19511,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19186,6 +19676,11 @@
       </c>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>ATOXIA 60 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-79D890D52529</t>
         </is>
       </c>
@@ -19209,7 +19704,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19370,6 +19865,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>ATOXIA 90 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-9CD626AAAD84</t>
         </is>
       </c>
@@ -19393,7 +19893,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19563,6 +20063,11 @@
         </is>
       </c>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>LAXILOSE SYRUP</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-45DC17228E12</t>
         </is>
@@ -19579,7 +20084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19625,100 +20130,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19750,7 +20260,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19765,92 +20275,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-84838</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>119.74</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>286</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19882,7 +20397,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19897,92 +20412,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-88195</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>228.97</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>287</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20014,7 +20534,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20029,92 +20549,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-94054</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>495.92</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>288</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20146,7 +20671,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20161,92 +20686,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-28605</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>426.89</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>289</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20278,7 +20808,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20293,92 +20823,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-53761</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>328.12</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>290</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20410,7 +20945,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20425,92 +20960,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-73163</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>255</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>291</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20542,7 +21082,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20557,92 +21097,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-72367</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>11.51</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>292</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20674,7 +21219,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20689,92 +21234,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-57569</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>53.5</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>293</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20806,7 +21356,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20821,92 +21371,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-59424</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>280.67</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>294</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20938,7 +21493,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20953,92 +21508,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-11234</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>236.74</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>295</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21070,7 +21630,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21085,92 +21645,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-88311</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>348.8</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>296</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21187,7 +21752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21293,6 +21858,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21328,7 +21903,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21393,6 +21968,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-DA214C3EC07E</t>
         </is>
@@ -21429,7 +22014,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21494,6 +22079,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-D121F7B997D1</t>
         </is>
@@ -21530,7 +22125,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21595,6 +22190,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-3C4F0C036C4E</t>
         </is>
@@ -21631,7 +22236,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21696,6 +22301,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-D6D6E3CBED52</t>
         </is>
@@ -21732,7 +22347,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21797,6 +22412,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-89C6937DE232</t>
         </is>
@@ -21833,7 +22458,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21898,6 +22523,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-84B3885238EF</t>
         </is>
@@ -21934,7 +22569,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21999,6 +22634,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-EB36D430500E</t>
         </is>
@@ -22035,7 +22680,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22100,6 +22745,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-8E39E713B58E</t>
         </is>
@@ -22136,7 +22791,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22201,6 +22856,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-C3BD03C76DE2</t>
         </is>
@@ -22237,7 +22902,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22302,6 +22967,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-659A6ACE52F1</t>
         </is>
@@ -22338,7 +23013,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22403,6 +23078,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-98DEFC6F56C6</t>
         </is>
@@ -22439,7 +23124,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22504,6 +23189,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-1A3BEF45B0AE</t>
         </is>
@@ -22540,7 +23235,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22605,6 +23300,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-CA1E08DD53BE</t>
         </is>
@@ -22641,7 +23346,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22706,6 +23411,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-D0A6721D9F28</t>
         </is>
@@ -22742,7 +23457,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22807,6 +23522,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-226A2BF8F7BD</t>
         </is>
@@ -22843,7 +23568,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22908,6 +23633,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-0621AF8982C0</t>
         </is>
@@ -22944,7 +23679,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -23009,6 +23744,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-76F218ACF244</t>
         </is>
@@ -23045,7 +23790,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23110,6 +23855,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-425C9351A6C5</t>
         </is>
@@ -23146,7 +23901,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23211,6 +23966,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-2DAE3C9A73F4</t>
         </is>
@@ -23247,7 +24012,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23312,6 +24077,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-9A457385E12D</t>
         </is>

--- a/product_upload/packages/34/file.xlsx
+++ b/product_upload/packages/34/file.xlsx
@@ -1271,8 +1271,16 @@
           <t>0812387443-680-227313872632</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ORATANE 10 mg Soft Capsules</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ORATANE 10 mg Soft Capsules detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1864,8 +1872,16 @@
           <t>2128003682-592-164280465682</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZOLONIA 5 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ZOLONIA 5 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -2835,8 +2851,16 @@
           <t>5600967319-027-625078518707</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ORATANE 20 mg Soft Capsules</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ORATANE 20 mg Soft Capsules detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -3022,8 +3046,16 @@
           <t>1609621741-439-843518918974</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CERUXIM 500 mg Film Coted Tablet</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>CERUXIM 500 mg Film Coted Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3213,8 +3245,16 @@
           <t>2733743817-866-971405332586</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VILTIN 50 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>VILTIN 50 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3408,8 +3448,16 @@
           <t>5634435678-224-203194162434</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EXTEMENT 25 mg Chewable Tablet</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>EXTEMENT 25 mg Chewable Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3603,8 +3651,16 @@
           <t>2217962736-331-378495783193</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SOLIQUA SOLOSTAR (33 mcg/ml) /100 U Solution for Injection</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>SOLIQUA SOLOSTAR (33 mcg/ml) /100 U Solution for Injection detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -4005,8 +4061,16 @@
           <t>3119420272-960-811725657171</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SOLIQUA SOLOSTAR 50 mcg/ml) /100 U Solution for Injection</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>SOLIQUA SOLOSTAR 50 mcg/ml) /100 U Solution for Injection detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4606,8 +4670,16 @@
           <t>7909940242-371-378048018852</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ INSTIGAR 30 mg Delayed-Release Capsule</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>INSTIGAR 30 mg Delayed-Release Capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>Jazeera Pharmaceutical Industries (JPI)</t>
@@ -5000,8 +5072,16 @@
           <t>0257993911-232-882338439327</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EZEACT 40 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>EZEACT 40 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>BATTERJEE PHARMACETICAL FACTORY</t>
@@ -5193,8 +5273,16 @@
           <t>5355495432-956-820368933511</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EZEACT 80 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>EZEACT 80 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>BATTERJEE PHARMACETICAL FACTORY</t>
@@ -6371,8 +6459,16 @@
           <t>0777484414-647-786184684903</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EXTEMENT 50 mg Chewable Tablet</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>EXTEMENT 50 mg Chewable Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6566,8 +6662,16 @@
           <t>3148265861-293-154863721493</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EXTEMENT 100 mg Chewable Tablet</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>EXTEMENT 100 mg Chewable Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6761,8 +6865,16 @@
           <t>5466946622-918-956365757407</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ IRBEGEN 150 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>IRBEGEN 150 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -6952,8 +7064,16 @@
           <t>1848111927-512-197618955929</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ IRBEGEN 300 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>IRBEGEN 300 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -7143,8 +7263,16 @@
           <t>6628872415-432-116757833122</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SEROGEN 25 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>SEROGEN 25 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7338,8 +7466,16 @@
           <t>9489799386-446-364088464299</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SEROGEN 100 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>SEROGEN 100 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7537,8 +7673,16 @@
           <t>2686546224-903-280498508764</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SEROGEN 200 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>SEROGEN 200 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7732,8 +7876,16 @@
           <t>3920728363-123-501558677134</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SEROGEN 300 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>SEROGEN 300 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -9113,8 +9265,16 @@
           <t>8642496390-281-591684535123</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AMEP 5 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>AMEP 5 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -9690,8 +9850,16 @@
           <t>1221319735-176-761944228113</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OCUDINE 0.2%  OPHTHALMIC SOLUTION</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>OCUDINE 0.2%  OPHTHALMIC SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -9877,8 +10045,16 @@
           <t>3144615394-292-913663600150</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NOSTAM 0.4 MG PROLONGED RELEASE TABLET</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>NOSTAM 0.4 MG PROLONGED RELEASE TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -10661,8 +10837,16 @@
           <t>5538848538-088-185944130266</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HEMLIBRA 150 MG/ML SOLUTION FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>HEMLIBRA 150 MG/ML SOLUTION FOR INJECTION detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -11246,8 +11430,16 @@
           <t>6245090732-782-349538668773</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZOLAN 5 MG FILM-COATED  TABLET</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>ZOLAN 5 MG FILM-COATED  TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -12014,8 +12206,16 @@
           <t>9848039510-159-459862843549</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CHLORASEPTIC SORE THROAT LOZENGES (cherry)</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>CHLORASEPTIC SORE THROAT LOZENGES (cherry) detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -12201,8 +12401,16 @@
           <t>0099580978-924-815834140695</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CHLORASEPTIC SORE THROAT LOZENGES (citrus)</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>CHLORASEPTIC SORE THROAT LOZENGES (citrus) detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12396,8 +12604,16 @@
           <t>5332064445-031-854068822924</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CHLORASEPTIC SORE THROAT LOZENGES ( Lemon)</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>CHLORASEPTIC SORE THROAT LOZENGES ( Lemon) detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -13379,8 +13595,16 @@
           <t>6877948286-555-176256596584</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VELIZA  500MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>VELIZA  500MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13771,8 +13995,16 @@
           <t>6409949972-831-264271391799</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ M.M.R II 0.5ML VACCINE+ 0.7ML DILUENT</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>M.M.R II 0.5ML VACCINE+ 0.7ML DILUENT detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -14356,8 +14588,16 @@
           <t>3850265870-719-491885860702</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Z FILL DEEP 2 IMPLANT IN PRE-FILLED SYRINGE</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Z FILL DEEP 2 IMPLANT IN PRE-FILLED SYRINGE detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -15140,8 +15380,16 @@
           <t>8318626152-621-845717273711</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CARPAZIO 150 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>CARPAZIO 150 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -15725,8 +15973,16 @@
           <t>3113710187-132-719244221410</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIBERZI 100 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>VIBERZI 100 MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -15916,8 +16172,16 @@
           <t>4132717232-112-790968740457</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIBERZI 75MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>VIBERZI 75MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -16298,8 +16562,16 @@
           <t>7766671777-529-306440723353</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXILANT 30 mg</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>DEXILANT 30 mg detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
           <t>BATTERJEE PHARMACETICAL FACTORY</t>
@@ -16491,8 +16763,16 @@
           <t>7897462244-428-170443333938</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Z FILL CONTOUR 2 IMPLANT IN PRE-FILLED SYRINGE</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Z FILL CONTOUR 2 IMPLANT IN PRE-FILLED SYRINGE detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -16670,8 +16950,16 @@
           <t>2647016503-179-911370462820</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Z FILL REFRESH 2 IMPLANT IN PRE-FILLED SYRINGE</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Z FILL REFRESH 2 IMPLANT IN PRE-FILLED SYRINGE detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16853,8 +17141,16 @@
           <t>1171390222-432-476394819390</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ESCITALAX 20MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ESCITALAX 20MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -17040,8 +17336,16 @@
           <t>6348935222-783-794437644482</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ESCITALAX 15MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>ESCITALAX 15MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -17227,8 +17531,16 @@
           <t>8517853195-566-970300249849</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ESCITALAX 10MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>ESCITALAX 10MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17613,8 +17925,16 @@
           <t>6748855876-537-973232754655</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Arkator 60MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Arkator 60MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17800,8 +18120,16 @@
           <t>0539571331-319-180932860380</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Arkator 90MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Arkator 90MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17987,8 +18315,16 @@
           <t>3888771735-982-547108881355</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Arkator 120MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Arkator 120MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -18174,8 +18510,16 @@
           <t>8180350334-340-746124391740</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STORVAS 40MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>STORVAS 40MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -18361,8 +18705,16 @@
           <t>9543849344-741-810952595710</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STORVAS 20MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>STORVAS 20MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -18548,8 +18900,16 @@
           <t>9848024712-094-913033696931</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STORVAS 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>STORVAS 10MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18739,8 +19099,16 @@
           <t>2808885404-499-889896389034</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EPIXX 100MG/ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>EPIXX 100MG/ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -19519,8 +19887,16 @@
           <t>9895496570-251-167943626802</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ATOXIA 60 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>ATOXIA 60 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -19712,8 +20088,16 @@
           <t>8850498807-623-920207882001</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ATOXIA 90 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>ATOXIA 90 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>

--- a/product_upload/packages/34/file.xlsx
+++ b/product_upload/packages/34/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20514,7 +20514,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22136,7 +22136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22217,40 +22217,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22330,38 +22335,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>270.09</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-DA214C3EC07E</t>
         </is>
@@ -22441,38 +22451,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>226.89</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-D121F7B997D1</t>
         </is>
@@ -22552,38 +22567,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>26.27</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-3C4F0C036C4E</t>
         </is>
@@ -22663,38 +22683,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>198.12</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-D6D6E3CBED52</t>
         </is>
@@ -22774,38 +22799,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>60.56</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-89C6937DE232</t>
         </is>
@@ -22885,38 +22915,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>177.73</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-84B3885238EF</t>
         </is>
@@ -22996,38 +23031,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>93.77</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-EB36D430500E</t>
         </is>
@@ -23107,38 +23147,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>341.85</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-8E39E713B58E</t>
         </is>
@@ -23218,38 +23263,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>310.34</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-C3BD03C76DE2</t>
         </is>
@@ -23329,38 +23379,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>59.2</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-659A6ACE52F1</t>
         </is>
@@ -23440,38 +23495,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>232.26</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-98DEFC6F56C6</t>
         </is>
@@ -23551,38 +23611,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>494.41</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-1A3BEF45B0AE</t>
         </is>
@@ -23662,38 +23727,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>349.19</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-CA1E08DD53BE</t>
         </is>
@@ -23773,38 +23843,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>226.39</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-D0A6721D9F28</t>
         </is>
@@ -23884,38 +23959,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>124.96</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-226A2BF8F7BD</t>
         </is>
@@ -23995,38 +24075,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>473.05</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-0621AF8982C0</t>
         </is>
@@ -24106,38 +24191,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>93.02</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-76F218ACF244</t>
         </is>
@@ -24217,38 +24307,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>173.8</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-425C9351A6C5</t>
         </is>
@@ -24328,38 +24423,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>168.42</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-2DAE3C9A73F4</t>
         </is>
@@ -24439,38 +24539,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>458.9</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-9A457385E12D</t>
         </is>
